--- a/public/downloads/CRM-LOOP-Case-B-Operations.xlsx
+++ b/public/downloads/CRM-LOOP-Case-B-Operations.xlsx
@@ -1021,7 +1021,7 @@
   <autoFilter ref="A5:O17"/>
   <tableColumns count="15">
     <tableColumn id="1" name="고객 ID"/>
-    <tableColumn id="2" name="시장"/>
+    <tableColumn id="2" name="선호 언어"/>
     <tableColumn id="3" name="고객군"/>
     <tableColumn id="4" name="초청 이유"/>
     <tableColumn id="5" name="RSVP"/>
@@ -1048,7 +1048,7 @@
     <tableColumn id="2" name="고객 ID"/>
     <tableColumn id="3" name="발생 구간"/>
     <tableColumn id="4" name="사유"/>
-    <tableColumn id="5" name="고객 선택권·다음 조치"/>
+    <tableColumn id="5" name="고객 선택권과 다음 조치"/>
     <tableColumn id="6" name="담당자"/>
     <tableColumn id="7" name="기한"/>
     <tableColumn id="8" name="상태"/>
@@ -1307,7 +1307,6 @@
       <c r="F3" s="156" t="n"/>
       <c r="G3" s="156" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -1525,8 +1524,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13"/>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="159" t="inlineStr">
         <is>
@@ -1590,7 +1587,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>customer_id / market / segment_code / selection_reason / suppression_status</t>
+          <t>customer_id / segment_code / selection_reason / suppression_status</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -1600,7 +1597,7 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>HQ CRM + Local CRM</t>
+          <t>CRM Manager</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -1836,8 +1833,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="159" t="inlineStr">
         <is>
@@ -1881,7 +1876,7 @@
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>초청 → RSVP</t>
+          <t>초청과 RSVP 사이</t>
         </is>
       </c>
       <c r="B27" s="20" t="n">
@@ -1894,7 +1889,7 @@
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>Local CRM</t>
+          <t>CRM Manager</t>
         </is>
       </c>
       <c r="E27" s="27" t="inlineStr">
@@ -1906,7 +1901,7 @@
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>응답 → 확정</t>
+          <t>응답과 확정 사이</t>
         </is>
       </c>
       <c r="B28" s="20" t="n">
@@ -1931,7 +1926,7 @@
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="20" t="inlineStr">
         <is>
-          <t>확정 → 참석</t>
+          <t>확정과 참석 사이</t>
         </is>
       </c>
       <c r="B29" s="20" t="n">
@@ -1956,7 +1951,7 @@
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="20" t="inlineStr">
         <is>
-          <t>참석 → 체험 완료</t>
+          <t>참석과 체험 완료 사이</t>
         </is>
       </c>
       <c r="B30" s="20" t="n">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>DIY 마감, 대기, 시간 부족 사유를 기록하고 대체 샘플 또는 재예약 제공</t>
+          <t>향 만들기 체험(DIY) 마감, 대기, 시간 부족 사유를 기록하고 대체 샘플 또는 재예약 제공</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -1981,7 +1976,7 @@
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="20" t="inlineStr">
         <is>
-          <t>참석 → 동의</t>
+          <t>참석과 동의 사이</t>
         </is>
       </c>
       <c r="B31" s="20" t="n">
@@ -2006,7 +2001,7 @@
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="20" t="inlineStr">
         <is>
-          <t>동의 → 후속 반응</t>
+          <t>동의와 후속 반응 사이</t>
         </is>
       </c>
       <c r="B32" s="20" t="n">
@@ -2031,7 +2026,7 @@
     <row r="33" ht="46" customHeight="1">
       <c r="A33" s="20" t="inlineStr">
         <is>
-          <t>후속 반응 → 관계 행동</t>
+          <t>후속 반응과 관계 행동 사이</t>
         </is>
       </c>
       <c r="B33" s="20" t="n">
@@ -2834,7 +2829,6 @@
       <c r="D3" s="156" t="n"/>
       <c r="E3" s="156" t="n"/>
     </row>
-    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="159" t="inlineStr">
         <is>
@@ -2886,7 +2880,7 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>정원표 / 인력표 / 서비스 복구 기준</t>
+          <t>정원표, 인력표, 서비스 복구 기준</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2892,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>공개 전후 메시지 범위, 엠바고, 필수 제품 정보, 시장별 표현</t>
+          <t>공개 전후 메시지 범위, 엠바고, 필수 제품 정보, 채널별 표현</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2908,7 +2902,7 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>콘텐츠 캘린더 / 메시지 승인본 / 반응 태그</t>
+          <t>콘텐츠 캘린더, 메시지 승인본, 반응 태그</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2924,7 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>제작물 목록 / 설치 위치 / 최종 승인 시점</t>
+          <t>제작물 목록, 설치 위치, 최종 승인 시점</t>
         </is>
       </c>
     </row>
@@ -3061,7 +3055,7 @@
       </c>
       <c r="B5" s="127" t="inlineStr">
         <is>
-          <t>시장</t>
+          <t>선호 언어</t>
         </is>
       </c>
       <c r="C5" s="127" t="inlineStr">
@@ -3138,7 +3132,7 @@
       </c>
       <c r="B6" s="130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C6" s="130" t="inlineStr">
@@ -3214,7 +3208,7 @@
       </c>
       <c r="B7" s="130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C7" s="130" t="inlineStr">
@@ -3290,7 +3284,7 @@
       </c>
       <c r="B8" s="130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C8" s="130" t="inlineStr">
@@ -3335,7 +3329,7 @@
       </c>
       <c r="K8" s="133" t="inlineStr">
         <is>
-          <t>Local CRM</t>
+          <t>CRM Manager</t>
         </is>
       </c>
       <c r="L8" s="133" t="inlineStr">
@@ -3362,7 +3356,7 @@
       </c>
       <c r="B9" s="130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>일본어</t>
         </is>
       </c>
       <c r="C9" s="130" t="inlineStr">
@@ -3438,7 +3432,7 @@
       </c>
       <c r="B10" s="130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C10" s="130" t="inlineStr">
@@ -3514,7 +3508,7 @@
       </c>
       <c r="B11" s="130" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="C11" s="130" t="inlineStr">
@@ -3554,7 +3548,7 @@
       </c>
       <c r="J11" s="133" t="inlineStr">
         <is>
-          <t>중문 사용 팁 발송</t>
+          <t>선호 언어로 사용 팁 발송</t>
         </is>
       </c>
       <c r="K11" s="133" t="inlineStr">
@@ -3590,7 +3584,7 @@
       </c>
       <c r="B12" s="130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C12" s="130" t="inlineStr">
@@ -3666,7 +3660,7 @@
       </c>
       <c r="B13" s="130" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>영어</t>
         </is>
       </c>
       <c r="C13" s="130" t="inlineStr">
@@ -3676,7 +3670,7 @@
       </c>
       <c r="D13" s="131" t="inlineStr">
         <is>
-          <t>시장별 반응 확인</t>
+          <t>신제품 콘텐츠 협업 후보</t>
         </is>
       </c>
       <c r="E13" s="132" t="inlineStr">
@@ -3711,7 +3705,7 @@
       </c>
       <c r="K13" s="133" t="inlineStr">
         <is>
-          <t>Local CRM</t>
+          <t>CRM Manager</t>
         </is>
       </c>
       <c r="L13" s="133" t="inlineStr">
@@ -3742,7 +3736,7 @@
       </c>
       <c r="B14" s="130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C14" s="130" t="inlineStr">
@@ -3818,7 +3812,7 @@
       </c>
       <c r="B15" s="130" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C15" s="130" t="inlineStr">
@@ -3894,7 +3888,7 @@
       </c>
       <c r="B16" s="130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>일본어</t>
         </is>
       </c>
       <c r="C16" s="130" t="inlineStr">
@@ -3970,7 +3964,7 @@
       </c>
       <c r="B17" s="136" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>한국어</t>
         </is>
       </c>
       <c r="C17" s="136" t="inlineStr">
@@ -4211,7 +4205,7 @@
       </c>
       <c r="C6" s="130" t="inlineStr">
         <is>
-          <t>초청 → RSVP</t>
+          <t>초청과 RSVP 사이</t>
         </is>
       </c>
       <c r="D6" s="130" t="inlineStr">
@@ -4226,7 +4220,7 @@
       </c>
       <c r="F6" s="130" t="inlineStr">
         <is>
-          <t>Local CRM</t>
+          <t>CRM Manager</t>
         </is>
       </c>
       <c r="G6" s="147" t="inlineStr">
@@ -4254,7 +4248,7 @@
       </c>
       <c r="C7" s="130" t="inlineStr">
         <is>
-          <t>확정 → 참석</t>
+          <t>확정과 참석 사이</t>
         </is>
       </c>
       <c r="D7" s="130" t="inlineStr">
@@ -4301,7 +4295,7 @@
       </c>
       <c r="C8" s="130" t="inlineStr">
         <is>
-          <t>참석 → 체험</t>
+          <t>참석과 체험 사이</t>
         </is>
       </c>
       <c r="D8" s="130" t="inlineStr">
@@ -4348,7 +4342,7 @@
       </c>
       <c r="C9" s="130" t="inlineStr">
         <is>
-          <t>참석 → 동의</t>
+          <t>참석과 동의 사이</t>
         </is>
       </c>
       <c r="D9" s="130" t="inlineStr">
@@ -4395,7 +4389,7 @@
       </c>
       <c r="C10" s="130" t="inlineStr">
         <is>
-          <t>동의 → 후속</t>
+          <t>동의와 후속 반응 사이</t>
         </is>
       </c>
       <c r="D10" s="130" t="inlineStr">
@@ -4438,7 +4432,7 @@
       </c>
       <c r="C11" s="130" t="inlineStr">
         <is>
-          <t>동의 → 후속</t>
+          <t>동의와 후속 반응 사이</t>
         </is>
       </c>
       <c r="D11" s="130" t="inlineStr">
@@ -4485,7 +4479,7 @@
       </c>
       <c r="C12" s="130" t="inlineStr">
         <is>
-          <t>후속 → 상담</t>
+          <t>후속 반응과 상담 사이</t>
         </is>
       </c>
       <c r="D12" s="130" t="inlineStr">
@@ -4528,7 +4522,7 @@
       </c>
       <c r="C13" s="136" t="inlineStr">
         <is>
-          <t>참석 → 체험</t>
+          <t>참석과 체험 사이</t>
         </is>
       </c>
       <c r="D13" s="136" t="inlineStr">

--- a/public/downloads/CRM-LOOP-Case-B-Operations.xlsx
+++ b/public/downloads/CRM-LOOP-Case-B-Operations.xlsx
@@ -1307,6 +1307,7 @@
       <c r="F3" s="156" t="n"/>
       <c r="G3" s="156" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="45" t="inlineStr">
         <is>
@@ -1524,6 +1525,8 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="159" t="inlineStr">
         <is>
@@ -1587,7 +1590,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>customer_id / segment_code / selection_reason / suppression_status</t>
+          <t>customer_id, segment_code, selection_reason, suppression_status</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -1624,7 +1627,7 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>rsvp_status / slot_id / party_size / language / accessibility_request</t>
+          <t>rsvp_status, slot_id, party_size, language, accessibility_request</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -1661,7 +1664,7 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>checkin_at / queue_enter_at / experience_start_at / no_show_reason</t>
+          <t>checkin_at, queue_enter_at, experience_start_at, no_show_reason</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -1698,7 +1701,7 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>scent_preference / diy_status / issue_reason / consult_request</t>
+          <t>scent_preference, diy_status, issue_reason, consult_request</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -1735,7 +1738,7 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>consent_status / consent_purpose / channel / consent_at / policy_version</t>
+          <t>consent_status, consent_purpose, channel, consent_at, policy_version</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -1772,7 +1775,7 @@
       </c>
       <c r="C21" s="20" t="inlineStr">
         <is>
-          <t>message_variant / sent_at / click_at / reply_type / handoff_status</t>
+          <t>message_variant, sent_at, click_at, reply_type, handoff_status</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -1809,7 +1812,7 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>outcome_type / outcome_at / order_value / revisit_at / opt_out_at</t>
+          <t>outcome_type, outcome_at, order_value, revisit_at, opt_out_at</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -1833,6 +1836,8 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="159" t="inlineStr">
         <is>
@@ -2176,7 +2181,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>JENTLE SALON / 2024</t>
+          <t>JENTLE SALON (2024)</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -2206,7 +2211,7 @@
       </c>
       <c r="H5" s="20" t="inlineStr">
         <is>
-          <t>참석률 / 피팅 참여율 / 상담 요청률</t>
+          <t>참석률, 피팅 참여율, 상담 요청률</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2223,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>JENTLE SALON / 2024</t>
+          <t>JENTLE SALON (2024)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -2228,7 +2233,7 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>개인 방문 후기 / 티스토리</t>
+          <t>티스토리 개인 방문 후기</t>
         </is>
       </c>
       <c r="E6" s="50" t="inlineStr">
@@ -2248,7 +2253,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>참석률 / 피팅 참여율 / 상담 요청률</t>
+          <t>참석률, 피팅 참여율, 상담 요청률</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2265,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>카디퓨저 성수 팝업 / 2024</t>
+          <t>카디퓨저 성수 팝업 (2024)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -2290,7 +2295,7 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>혜택 수령률 / 대체안 수락률 / 후속 반응 / 재방문</t>
+          <t>혜택 수령률, 대체안 수락률, 후속 반응, 재방문</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2307,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>카디퓨저 성수 팝업 / 2024</t>
+          <t>카디퓨저 성수 팝업 (2024)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -2312,7 +2317,7 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>개인 방문 후기 / 티스토리</t>
+          <t>티스토리 개인 방문 후기</t>
         </is>
       </c>
       <c r="E8" s="50" t="inlineStr">
@@ -2332,7 +2337,7 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>혜택 수령률 / 대체안 수락률 / 후속 반응 / 재방문</t>
+          <t>혜택 수령률, 대체안 수락률, 후속 반응, 재방문</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2349,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>카디퓨저 성수 팝업 / 2024</t>
+          <t>카디퓨저 성수 팝업 (2024)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -2354,7 +2359,7 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>개인 방문 후기 / Ameblo</t>
+          <t>Ameblo 개인 방문 후기</t>
         </is>
       </c>
       <c r="E9" s="50" t="inlineStr">
@@ -2374,7 +2379,7 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>혜택 수령률 / 대체안 수락률 / 후속 반응 / 재방문</t>
+          <t>혜택 수령률, 대체안 수락률, 후속 반응, 재방문</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2391,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>OMG! NU+JEANS / 2022–2023</t>
+          <t>OMG! NU+JEANS (2022–2023)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2416,7 +2421,7 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>동의율 / 품절 대체 수락 / 7일 후속 반응 / 예약</t>
+          <t>동의율, 품절 대체 수락, 7일 후속 반응, 예약</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2433,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>OMG! NU+JEANS / 2022–2023</t>
+          <t>OMG! NU+JEANS (2022–2023)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -2438,7 +2443,7 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>개인 방문 후기 / Lemon8</t>
+          <t>Lemon8 개인 방문 후기</t>
         </is>
       </c>
       <c r="E11" s="50" t="inlineStr">
@@ -2458,7 +2463,7 @@
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>동의율 / 품절 대체 수락 / 7일 후속 반응 / 예약</t>
+          <t>동의율, 품절 대체 수락, 7일 후속 반응, 예약</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2475,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>DESERT COWBOY / 2026</t>
+          <t>DESERT COWBOY (2026)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -2480,7 +2485,7 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>행사 소개 / 이데일리</t>
+          <t>이데일리 행사 소개</t>
         </is>
       </c>
       <c r="E12" s="50" t="inlineStr">
@@ -2500,7 +2505,7 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>피팅 완료율 / 문의 유형 / 재고 요청 / 인터뷰 표본 수</t>
+          <t>피팅 완료율, 문의 유형, 재고 요청, 인터뷰 표본 수</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2517,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>DESERT COWBOY / 2026</t>
+          <t>DESERT COWBOY (2026)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -2522,7 +2527,7 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>공간 소개 / 한국섬유신문</t>
+          <t>한국섬유신문 공간 소개</t>
         </is>
       </c>
       <c r="E13" s="50" t="inlineStr">
@@ -2542,7 +2547,7 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>피팅 완료율 / 문의 유형 / 재고 요청 / 인터뷰 표본 수</t>
+          <t>피팅 완료율, 문의 유형, 재고 요청, 인터뷰 표본 수</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2559,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>하우스 노웨어 서울 첫 매장 / 2025</t>
+          <t>하우스 노웨어 서울 첫 매장 (2025)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -2584,7 +2589,7 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>층간 이동 선택 / 제품 상담 / 후속 동의 / 재방문</t>
+          <t>층간 이동 선택, 제품 상담, 후속 동의, 재방문</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2601,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>하우스 노웨어 서울 첫 매장 / 2025</t>
+          <t>하우스 노웨어 서울 첫 매장 (2025)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -2606,7 +2611,7 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>에디터 방문기 / 성수동고릴라</t>
+          <t>성수동고릴라 에디터 방문기</t>
         </is>
       </c>
       <c r="E15" s="50" t="inlineStr">
@@ -2626,7 +2631,7 @@
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>층간 이동 선택 / 제품 상담 / 후속 동의 / 재방문</t>
+          <t>층간 이동 선택, 제품 상담, 후속 동의, 재방문</t>
         </is>
       </c>
     </row>
@@ -2829,6 +2834,7 @@
       <c r="D3" s="156" t="n"/>
       <c r="E3" s="156" t="n"/>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="159" t="inlineStr">
         <is>
